--- a/tools/excelc/examples/ExampleEN.xlsx
+++ b/tools/excelc/examples/ExampleEN.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{464946AB-AA56-4265-83C1-7347E15861D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{8FAFC883-4A22-4226-957C-4441C87A6F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="@types" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="98">
   <si>
     <t>ObjectType</t>
   </si>
@@ -190,7 +190,16 @@
     <t>unique_index=1</t>
   </si>
   <si>
+    <t>scope=c&amp;scope=s</t>
+  </si>
+  <si>
+    <t>scope=c</t>
+  </si>
+  <si>
     <t>unique_index=2</t>
+  </si>
+  <si>
+    <t>scope=s</t>
   </si>
   <si>
     <t>separator=|</t>
@@ -837,7 +846,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="14.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
@@ -973,76 +982,85 @@
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -1071,34 +1089,34 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L5" s="2">
         <v>1</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -1127,34 +1145,34 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -1183,34 +1201,34 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -1239,34 +1257,34 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excelc/examples/ExampleEN.xlsx
+++ b/tools/excelc/examples/ExampleEN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="@types" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="151">
   <si>
     <t>ObjectType</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Object tags</t>
   </si>
   <si>
-    <t>EnumEN</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>raw_data</t>
   </si>
   <si>
-    <t>object</t>
-  </si>
-  <si>
     <t>quality</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
   </si>
   <si>
     <t>ExampleObjectEN[]</t>
-  </si>
-  <si>
-    <t>EnumEN[]</t>
   </si>
   <si>
     <t>map&lt;int32, string&gt;</t>
@@ -497,12 +488,32 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>single_object</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExampleObjectEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExampleEnumEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExampleEnumEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExampleEnumEN[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +546,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -586,7 +604,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -603,6 +621,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -969,8 +990,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
+      <c r="A4" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -989,54 +1010,54 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1051,567 +1072,567 @@
   <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="58" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="34.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="62.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="78.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="83.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="67.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="34.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="62.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="78.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="83.75" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="58" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="X1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="R2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="2" t="s">
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="2" t="s">
+      <c r="W2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V3" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:25" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="5" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>1</v>
+      <c r="A5" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1">
         <v>101</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>201</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>32</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>64</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>-42</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>1.25</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>2.5</v>
       </c>
-      <c r="N5" s="1" t="b">
+      <c r="O5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="R5" s="1">
+    </row>
+    <row r="6" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T5" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="S6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+      <c r="U6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="81" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T6" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="V6" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="81" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y7" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="1">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="1">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="Y11" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y14" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y15" s="1" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="B17" s="1">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1">
         <v>6</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>12</v>
-      </c>
-      <c r="B17" s="1">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>135</v>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1643,36 +1664,36 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1">
         <v>13</v>
@@ -1681,7 +1702,7 @@
         <v>200</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F5" s="1">
         <v>7</v>
@@ -1690,15 +1711,15 @@
         <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1">
         <v>14</v>
@@ -1707,7 +1728,7 @@
         <v>200</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F6" s="1">
         <v>7</v>
@@ -1734,42 +1755,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
